--- a/output/pdf_financials_xlsx/CCI.xlsx
+++ b/output/pdf_financials_xlsx/CCI.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCI.xlsx
+++ b/output/pdf_financials_xlsx/CCI.xlsx
@@ -480,10 +480,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -514,10 +512,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -584,10 +580,10 @@
         <v>0.552381</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>88.869899</v>
+        <v>0.165516</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>102.574799</v>
+        <v>0.26335</v>
       </c>
     </row>
     <row r="11">
@@ -596,16 +592,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.552381</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-88.869899</v>
+        <v>-0.165516</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-102.574799</v>
+        <v>-0.26335</v>
       </c>
     </row>
     <row r="12">
@@ -631,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -678,10 +672,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>4.267948</v>
@@ -697,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -756,10 +748,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>4.267948</v>
@@ -806,10 +796,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>4.267948</v>
@@ -856,10 +844,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>55.88055</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>85.35896</v>
@@ -874,10 +860,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>4.267948</v>
@@ -908,10 +892,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>4.267948</v>
@@ -948,10 +930,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
@@ -4041,7 +4021,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Loan payable(note 8)</t>
+          <t>Loan payable (note 8)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4900,24 +4880,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation expenditures (note 5) $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>0.448782</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>88.869899</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>102.574799</v>
+        <v>0.375585</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4933,15 +4909,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (note 5) $</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Professional and regulatory fees</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
-        <v>0.448782</v>
+        <v>0.263153</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.375585</v>
+        <v>0.267949</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4962,7 +4942,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Professional and regulatory fees</t>
+          <t>Salaries, benefits and consulting fees</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4971,10 +4951,10 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.263153</v>
+        <v>0.289228</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.267949</v>
+        <v>0.188869</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4995,19 +4975,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salaries, benefits and consulting fees</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.289228</v>
+        <v>0.121088</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.188869</v>
+        <v>0.027522</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5028,19 +5008,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.121088</v>
+        <v>0.001422</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.027522</v>
+        <v>0.00063</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5061,15 +5037,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Stock-based payments (note 10)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.001422</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.00063</v>
+        <v>0.021406</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5090,17 +5068,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stock-based payments (note 10)</t>
+          <t>Travel expenditure</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>0.021406</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012628</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.017246</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5121,15 +5097,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Travel expenditure</t>
+          <t>Net loss for before other items:</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>0.012628</v>
+        <v>-1.157707</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.017246</v>
+        <v>-0.8778010000000001</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5145,20 +5121,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net loss for before other items:</t>
+          <t>Gain on disposition of exploration and evaluation assets (note 5)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-1.157707</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.8778010000000001</v>
+        <v>0.348186</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5179,17 +5157,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain on disposition of exploration and evaluation assets (note 5)</t>
+          <t>Impairment of exploration and evaluation assets (note 5)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>-0.01323</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.348186</v>
+        <v>-0.30722</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5210,15 +5186,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (note 5)</t>
+          <t>Reversal of flow-through liability (note 10(b)(ii))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>-0.01323</v>
+        <v>0.038337</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.30722</v>
+        <v>0.022863</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5239,15 +5215,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reversal of flow-through liability (note 10(b)(ii))</t>
+          <t>Accretion of provision for closure and reclamation</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.038337</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.022863</v>
+        <v>-0.07718</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5268,17 +5246,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Accretion of provision for closure and reclamation</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0.014989</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.07718</v>
+        <v>0.001131</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5299,19 +5279,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Other income (note 5(a))</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0.014989</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.001131</v>
+        <v>0.01821</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5332,7 +5314,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Other income (note 5(a))</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5346,7 +5328,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.01821</v>
+        <v>-0.058064</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5367,21 +5349,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest expense on loan payables (notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.058064</v>
+        <v>-0.142282</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5402,17 +5380,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Interest expense on loan payables (notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-1.117611</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.142282</v>
+        <v>-1.072157</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5428,7 +5408,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $ (1,072,157) $(1,117,611)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCI.xlsx
+++ b/output/pdf_financials_xlsx/CCI.xlsx
@@ -676,10 +676,10 @@
         <v>-1.117611</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="17">
@@ -752,10 +752,10 @@
         <v>-1.117611</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="21">
@@ -800,10 +800,10 @@
         <v>-1.117611</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="24">
@@ -848,10 +848,10 @@
         <v>55.88055</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>85.35896</v>
+        <v>-85.35896</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>89.64533299999999</v>
+        <v>-89.64533299999999</v>
       </c>
     </row>
     <row r="27">
@@ -864,10 +864,10 @@
         <v>-1.117611</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-1.117611</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="30">
@@ -934,10 +934,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3545,7 +3545,11 @@
           <t>Reserves 12, 13 867,751</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.515659</v>
       </c>
@@ -4828,10 +4832,10 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>4.267948</v>
+        <v>-4.267948</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>2.68936</v>
+        <v>-2.68936</v>
       </c>
     </row>
     <row r="59">

--- a/output/pdf_financials_xlsx/CCI.xlsx
+++ b/output/pdf_financials_xlsx/CCI.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.014989</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001131</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012979</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.117611</v>
+        <v>-1.1326</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.267948</v>
+        <v>-4.266817</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.68936</v>
+        <v>-2.676381</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.117611</v>
+        <v>-1.1326</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.267948</v>
+        <v>-4.266817</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.68936</v>
+        <v>-2.676381</v>
       </c>
     </row>
     <row r="30">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.343667</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.145386</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.343667</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.145386</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.359433</v>
+        <v>0.015766</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.252135</v>
+        <v>0.106749</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
